--- a/в бланки заводов/Мираторг КИ/miratorg_ki/my_lib/1C.xlsx
+++ b/в бланки заводов/Мираторг КИ/miratorg_ki/my_lib/1C.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Тестирование\miratorg_ki\my_lib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Мираторг КИ\miratorg_ki\my_lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9F8144-841D-46CA-A3A2-CA0D9DC679C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08157F74-C33F-4A15-A30B-65165BCB7C70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/в бланки заводов/Мираторг КИ/miratorg_ki/my_lib/1C.xlsx
+++ b/в бланки заводов/Мираторг КИ/miratorg_ki/my_lib/1C.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Мираторг КИ\miratorg_ki\my_lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08157F74-C33F-4A15-A30B-65165BCB7C70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6C737A-B5CF-4214-9FED-F2E2AB01CC71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>1С</t>
   </si>
@@ -136,6 +139,75 @@
   </si>
   <si>
     <t>Сервелат Мраморный в/к ВУ ОХЛ 330г*6</t>
+  </si>
+  <si>
+    <t>Ветчина Парма с/к нарезка ОХЛ ГЗМС 100г*10 (1,0 кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Ветчина Сочная ОХЛ ПА 400г*6 (2,4 кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>КП Колбаса с/к Neapolitano ВУ ОХЛ 250г*6</t>
+  </si>
+  <si>
+    <t>Колбаса в/к Черная Бергамо ВУ ОХЛ 280г*6 (1,68 кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Колбаса вареная "Филейная" п/а ОХЛ 350г*6 (2,1кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>МХБ Колбаса сырокопченая «Салями» нарезка ШТ. охл ГЗМС 100г*10 (1,0 кг) МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>МХБ Сосиски Сочные ШТ. п/а ОХЛ 350г*6 (2,1кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Прошутто с/к нарезка ОХЛ ГЗМС 100г*10 (1,0 кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Ребрышки свиные томленые ОХЛ ВУ 500г*4 (2,0кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Сосиски "Итальянские с сыром" ОХЛГЗМС 350г*6 (2,1кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Сосиски "Оригинальные" п/а ОХЛ ГЗМС 350г*6 (2,1кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>Сосиски Нежные п/а охл 350г*6 (2,1кг)  МИРАТОРГ</t>
+  </si>
+  <si>
+    <t>МХБ Ветчина Парма ск нар ГЗМС 100г*10</t>
+  </si>
+  <si>
+    <t>МХБ Ветчина Сочная п/а ОХЛ 400*6 (2,4 кг )ООО "Мираторг-Курск" РОССИЯ</t>
+  </si>
+  <si>
+    <t>КП Колб вк Черная Бергамо ВУ ОХЛ 280г*6</t>
+  </si>
+  <si>
+    <t>МХБ Колбаса Филейная охл п/а 350*6</t>
+  </si>
+  <si>
+    <t>МХБ Колбаса ск Салями нар охл 100г*10</t>
+  </si>
+  <si>
+    <t>МХБ Сосиски Сочные охл п/а 350*6</t>
+  </si>
+  <si>
+    <t>МХБ Прошутто ск нар ГЗМС 100г*10</t>
+  </si>
+  <si>
+    <t>КП Ребрышки свиные томленые ОХЛ ВУ 500г</t>
+  </si>
+  <si>
+    <t>КП Сосиски Ита с сыром ОХЛ ГЗМС 350г*6</t>
+  </si>
+  <si>
+    <t>МХБ Сосис "Оригинальные" п/а ОХЛ ГЗМС 350*6</t>
+  </si>
+  <si>
+    <t>МХБ Сосиски Нежные п/а охл 350г*6 (45)</t>
   </si>
 </sst>
 </file>
@@ -454,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
@@ -649,7 +721,140 @@
         <v>34</v>
       </c>
     </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1010032041</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1010023293</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1010032755</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1010032754</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1010030635</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1010031576</v>
+      </c>
+      <c r="C23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1010031142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1010032043</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1010033903</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1010032675</v>
+      </c>
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1010031149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1010031327</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{886269BE-0E73-4B63-A0C0-74C8ACE2CAA1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>